--- a/Tagihan/2026/Juli/PT. Mizan.xlsx
+++ b/Tagihan/2026/Juli/PT. Mizan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\2026\Juli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C038B321-9F78-4DF6-8259-1B0AC0552717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20D8CEB-093A-4067-A746-9A6958D73E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Satu Desa" sheetId="1" r:id="rId1"/>
@@ -639,6 +639,18 @@
     <xf numFmtId="42" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -694,17 +706,11 @@
     <xf numFmtId="15" fontId="11" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="11" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -723,12 +729,6 @@
     </xf>
     <xf numFmtId="42" fontId="12" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1268,47 +1268,47 @@
     <row r="5" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
     </row>
     <row r="8" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
     </row>
     <row r="9" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
     </row>
     <row r="10" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
     </row>
     <row r="11" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
     </row>
     <row r="12" spans="2:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F12" s="12"/>
@@ -1318,20 +1318,20 @@
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="43" t="s">
+      <c r="F13" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="43"/>
+      <c r="G13" s="47"/>
     </row>
     <row r="14" spans="2:7" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="44" t="s">
+      <c r="F14" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="44"/>
+      <c r="G14" s="48"/>
     </row>
     <row r="15" spans="2:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C15" s="7"/>
@@ -1358,12 +1358,12 @@
       </c>
     </row>
     <row r="17" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="46">
+      <c r="B17" s="50">
         <v>46212</v>
       </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="48"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="52"/>
       <c r="F17" s="22"/>
       <c r="G17" s="23"/>
     </row>
@@ -1418,12 +1418,12 @@
       <c r="G20" s="24"/>
     </row>
     <row r="21" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="49">
+      <c r="B21" s="53">
         <v>46216</v>
       </c>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="51"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="55"/>
       <c r="F21" s="24"/>
       <c r="G21" s="24"/>
     </row>
@@ -1473,13 +1473,13 @@
       <c r="G25" s="23"/>
     </row>
     <row r="26" spans="2:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="38" t="s">
+      <c r="B26" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="40"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="44"/>
       <c r="G26" s="26">
         <f>SUM(G17:G25)</f>
         <v>8250000</v>
@@ -1494,45 +1494,45 @@
       <c r="G27" s="16"/>
     </row>
     <row r="29" spans="2:7" s="18" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="41"/>
+      <c r="C29" s="45"/>
       <c r="D29" s="30"/>
       <c r="E29" s="17"/>
-      <c r="F29" s="42" t="s">
+      <c r="F29" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="42"/>
+      <c r="G29" s="46"/>
     </row>
     <row r="33" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="55"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="36" t="s">
+      <c r="B34" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
       <c r="F34" s="19"/>
       <c r="G34" s="21"/>
       <c r="H34" s="20"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="33" t="s">
+      <c r="B35" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
       <c r="H35" s="20"/>
     </row>
   </sheetData>
@@ -1553,7 +1553,7 @@
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B21:E21"/>
   </mergeCells>
-  <pageMargins left="0.39370078740157483" right="0.23622047244094491" top="7.874015748031496E-2" bottom="0.74803149606299213" header="0.59055118110236227" footer="0.31496062992125984"/>
+  <pageMargins left="0.31" right="0.23622047244094491" top="7.874015748031496E-2" bottom="0.74803149606299213" header="0.59055118110236227" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="85" orientation="portrait" horizontalDpi="4294967294" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -1577,47 +1577,47 @@
     <row r="5" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
     </row>
     <row r="8" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
     </row>
     <row r="9" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
     </row>
     <row r="10" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
     </row>
     <row r="11" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
     </row>
     <row r="12" spans="2:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F12" s="12"/>
@@ -1627,20 +1627,20 @@
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="43" t="s">
+      <c r="F13" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="43"/>
+      <c r="G13" s="47"/>
     </row>
     <row r="14" spans="2:7" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="44" t="s">
+      <c r="F14" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="44"/>
+      <c r="G14" s="48"/>
     </row>
     <row r="15" spans="2:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C15" s="7"/>
@@ -1667,12 +1667,12 @@
       </c>
     </row>
     <row r="17" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="46">
+      <c r="B17" s="50">
         <v>46152</v>
       </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="48"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="52"/>
       <c r="F17" s="22"/>
       <c r="G17" s="23"/>
     </row>
@@ -1748,12 +1748,12 @@
       <c r="G21" s="23"/>
     </row>
     <row r="22" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="49">
+      <c r="B22" s="53">
         <v>46183</v>
       </c>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="63"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="57"/>
       <c r="F22" s="24"/>
       <c r="G22" s="24"/>
     </row>
@@ -1808,38 +1808,38 @@
       <c r="G25" s="23"/>
     </row>
     <row r="26" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="59" t="s">
+      <c r="B26" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="61"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="63"/>
       <c r="G26" s="32">
         <f>SUM(G18:G25)</f>
         <v>3685000</v>
       </c>
     </row>
     <row r="27" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="56" t="s">
+      <c r="B27" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="58"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="60"/>
       <c r="G27" s="23">
         <v>500000</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="40"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="44"/>
       <c r="G28" s="26">
         <f>G26-G27</f>
         <v>3185000</v>
@@ -1854,57 +1854,49 @@
       <c r="G29" s="16"/>
     </row>
     <row r="31" spans="2:7" s="18" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="41"/>
+      <c r="C31" s="45"/>
       <c r="D31" s="30"/>
       <c r="E31" s="17"/>
-      <c r="F31" s="42" t="s">
+      <c r="F31" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="42"/>
+      <c r="G31" s="46"/>
     </row>
     <row r="35" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="55"/>
-      <c r="C35" s="55"/>
-      <c r="D35" s="55"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="55"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="36" t="s">
+      <c r="B36" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
       <c r="F36" s="19"/>
       <c r="G36" s="21"/>
       <c r="H36" s="20"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="33" t="s">
+      <c r="B37" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
       <c r="H37" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="F31:G31"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="B27:F27"/>
@@ -1914,8 +1906,17 @@
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="F13:G13"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="F31:G31"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.16" right="0.15" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="85" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>